--- a/AAII_Financials/Quarterly/XPEV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/XPEV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="92">
   <si>
     <t>XPEV</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2906500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1889700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3181700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2862800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2550900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2178800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2206400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1440100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1116200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>906900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1840400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1169000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>698100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>587200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>724700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>942700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1033800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1036400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1178800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>813100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>534700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>423800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>396900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>293300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>87100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>65000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>98500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>69200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>174700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13500</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2305400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1500700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2488100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2286300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2108800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1839900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1869100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1220400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>959900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>790000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1714800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1200200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>725300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>577400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>661900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>815200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>921300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>909800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1010700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>696400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>470900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>376400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>354200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>274600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>89500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>68100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>88200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>144200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>239900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>20200</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>601100</v>
+      </c>
+      <c r="E10" s="3">
         <v>388900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>693600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>576500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>442100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>338900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>337300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>219800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>156300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>116900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>125700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-31200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-27200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>62700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>127600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>112500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>126600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>168100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>116700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>63800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>47400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>42700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>18700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>10400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-75000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-65200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-6700</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>429000</v>
+      </c>
+      <c r="E12" s="3">
         <v>421500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>410900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>341200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>308000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>273000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>274900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>232800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>201800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>187000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>184400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>179000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>188500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>188600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>173400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>207000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>175900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>169800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>200000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>179700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>122700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>76900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>64000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>93600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>47100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>49000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>100400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>67000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>77800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>72500</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,53 +1338,56 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-31900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-28100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-8000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-8200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-10600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>54000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-21600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>33500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1377,36 +1397,36 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>27100</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
         <v>13400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5200</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="3">
         <v>16900</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1419,53 +1439,56 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E15" s="3">
         <v>82500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>81300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>75800</v>
       </c>
-      <c r="G15" s="3">
-        <v>75400</v>
-      </c>
       <c r="H15" s="3">
+        <v>67900</v>
+      </c>
+      <c r="I15" s="3">
         <v>67100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>66700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>68600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>66200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>66700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>67900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>35300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>50300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>37500</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,193 +1576,197 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3081800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2168800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3178200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2957900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2686200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2306000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2428800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1680300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1339900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1159100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2122600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1602200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1124200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>963500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1079600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1243500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1324500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1303400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1513600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1069300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>739800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>553600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>553000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>550300</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD17" s="3">
         <v>265800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>186500</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG17" s="3">
-        <v>0</v>
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-175200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-279200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-95100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-135200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-127200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-222400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-240200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-223700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-252200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-282100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-433200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-426100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-376400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-354900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-290700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-267000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-334800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-256200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-205100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-129800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-156100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-257000</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-167200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-117300</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1746,8 +1776,11 @@
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,95 +1815,96 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E20" s="3">
         <v>23400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-26500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-19800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-90700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>132200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>27100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-19600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-79600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>33600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>162900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>31900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>38700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>17000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>47000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>88300</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="3">
         <v>15200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-700</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1880,62 +1914,65 @@
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-102100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-220200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>84500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-15000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-33300</v>
-      </c>
       <c r="H21" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-40400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-160500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-167500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-150400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-187600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-123600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-530000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-362600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-337500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-189500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-306600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1948,27 +1985,27 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-63400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-137000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-100400</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,264 +2015,273 @@
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E22" s="3">
         <v>23900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>800</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-185900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-257300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>58000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-54500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-68000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-90400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-188300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-256700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-181400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-189300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-187000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-532600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-385600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-339300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-335000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-325800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-373400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-236100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-173800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-226700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-169800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-113000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-109400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-169300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-102500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-153500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-119500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-190600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-102500</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-6000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3500</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -2243,11 +2289,11 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
@@ -2266,14 +2312,17 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
+      <c r="AG24" s="3">
+        <v>0</v>
       </c>
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-196800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-258700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>54800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-53500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-66700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-91500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-182200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-257700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-176800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-189400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-190000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-532700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-386700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-340200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-333500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-328700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-375000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-236400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-177300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-226700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-169800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-113000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-109600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-169300</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-153500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-119500</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG26" s="3">
-        <v>0</v>
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-196800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-258700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>54800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-53500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-66700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-91500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-182200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-257700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-176800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-189400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-190000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-532700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-386700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-340200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-332900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-328300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-375500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-236400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-177300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-226700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-169800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-113000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-109600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-298500</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-208600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-151300</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG27" s="3">
-        <v>0</v>
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,95 +3025,98 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-23400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>26500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>19800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>90700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-132200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-27100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>19600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>79600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-33600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-162900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-31900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-38700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-17000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-47000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-88300</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-15200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>700</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-196800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-258700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>54800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-53500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-66700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-91500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-182200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-257700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-176800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-189400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-190000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-532700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-386700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-340200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-332900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-328300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-375500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-236400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-177300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-226700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-169800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-113000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-109600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-298500</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-208600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-151300</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG33" s="3">
-        <v>0</v>
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-196800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-258700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>54800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-53500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-66700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-91500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-182200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-257700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-176800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-189400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-190000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-532700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-386700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-340200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-332900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-328300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-375500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-236400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-177300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-226700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-169800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-113000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-109600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-298500</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-208600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-151300</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG35" s="3">
-        <v>0</v>
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,86 +3611,87 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2096100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2096500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2477600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2462800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2625600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2447300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2546400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1519800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1961400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2014200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2979500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1671700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1518200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1284900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4163100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4081700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4151800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4605800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5081700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5486300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4066100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4603000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4202300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1800900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>156400</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,86 +3710,89 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2032200</v>
+      </c>
+      <c r="E42" s="3">
         <v>2339200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2536600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2653200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2253000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2187100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1950500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2339600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1910800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2642500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2498800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2305200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2306600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2307200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>177900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>278900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>340500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>300300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>390400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>482400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>128300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>210900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>392600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>850000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>32900</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,86 +3811,89 @@
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>741200</v>
+      </c>
+      <c r="E43" s="3">
         <v>639600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>814500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>642000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>626700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>636600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>700600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>654800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>569900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>556100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>657000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>681100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>719400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>755600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>194600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>176100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>743100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>151600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>561800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>379400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>296100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>234000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>251600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>217500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>191500</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3819,86 +3912,89 @@
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2021100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1927100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1484100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1298000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>921700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>822600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>762100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>875700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>765900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>850400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>779300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>724700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>492500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>629600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>637400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>604900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>589400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>510300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>366800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>327900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>301500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>277600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>186900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>126900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>114100</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3917,86 +4013,89 @@
       <c r="AH44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1144500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1005200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>862500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>706700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>586000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>469900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>422300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>483900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>472900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>476300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>326600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>444400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>434600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>517900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>417500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>417400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>249900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>402000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>327100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>469500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>438400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>512300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>489800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>432600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>193100</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4015,86 +4114,89 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9054500</v>
+      </c>
+      <c r="E46" s="3">
         <v>8795700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9043500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8421500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7645500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7167600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6814000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6268500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6155700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6963200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7689000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5983300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5564500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5540600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6136500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6070700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6074700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6398100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6727900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7145500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5230500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5837800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5523400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3427800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>688000</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4113,86 +4215,89 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>813200</v>
+      </c>
+      <c r="E47" s="3">
         <v>894900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>970300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1058500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1144600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1008300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>884000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>809400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>822600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>769700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>722100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>967100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>880100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1433600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1608600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1736300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1789200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1334200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>913500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>557000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>468100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>231700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>55500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>15500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>16600</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4211,86 +4316,89 @@
       <c r="AH47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2803900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2698000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2467400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2263800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2198700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2114700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1751400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1804900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1615400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1661800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1750200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1709300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1812000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1862900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1770900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1579900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1288500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1103900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>962500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>824800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>648500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>551000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>493100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>517300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>533500</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4309,86 +4417,89 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1098300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1103500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1072800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1046700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1059300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1064200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1012300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1044800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1027900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1053900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1096100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>526600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>537400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>560600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>147000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>123300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>120000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>122800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>203100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>206900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>176000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>141700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>119400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>126500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>127600</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,86 +4720,89 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>280400</v>
+      </c>
+      <c r="E52" s="3">
         <v>273300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>238700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>342700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>214100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>305700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>231900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>333500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>260500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>188200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>155800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>123000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>89000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>104300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>415800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>408300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>359000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>353100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>238400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>21700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>57800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>31800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8400</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,86 +4922,89 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14955000</v>
+      </c>
+      <c r="E54" s="3">
         <v>14616000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14749300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13808600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12901900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12249600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11331000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10896700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10320600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11065100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11869100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9667900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9195000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9820500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10078800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9918500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9631500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9312200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9045400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8755900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6580900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6774700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6223200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4096100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1374100</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4897,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,86 +5099,87 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4374500</v>
+      </c>
+      <c r="E57" s="3">
         <v>4479200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5313300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4931700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4283600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3718500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3162100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2404200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2255400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2773300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3132200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2270400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1559000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1666600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2005100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2072300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1269500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1925400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1703300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1256700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>917900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>847000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>711600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>514600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>233400</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5067,86 +5198,89 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1642500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1154900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1116800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>824700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>829200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>896100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>936300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>991600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>893500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>906900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>873700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>750800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>822500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>710200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>466600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>289200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1010000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>66400</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>8100</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>1100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>24100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>41300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>49700</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5165,86 +5299,89 @@
       <c r="AH58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>289200</v>
+      </c>
+      <c r="E59" s="3">
         <v>291300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1047900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>268200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>209100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>164300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>772400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>124200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>123500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>77900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>620900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>215800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>543900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>68200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>928000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>855100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>798600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>797700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>778500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>581000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>433400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>453900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>355300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>318300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>326400</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5263,86 +5400,89 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8141800</v>
+      </c>
+      <c r="E60" s="3">
         <v>7732400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8308600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7524500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6695300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5915700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5461600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4565600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4100300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4638900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5092700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4151400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3231000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3294800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3399700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3216600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3078100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2789500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2481800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1845800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1351300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1302000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1090900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>874200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>609500</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5361,86 +5501,89 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2311500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2278600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1678800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1611100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1536200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1543200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1247300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1206200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1035300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1053500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1296800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1200000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1265200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1408500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1011400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>549700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>603700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>313700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>230800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>188200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>226900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>229800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>229000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>245700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>249000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5459,86 +5602,89 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>277600</v>
+      </c>
+      <c r="E62" s="3">
         <v>246000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>171200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>266200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>242700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>391300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>150100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>408400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>363600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>359000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>187800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>277200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>60600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
         <v>464100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>703000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>391900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>575800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>290600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>479600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>409300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>383500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>110600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>69100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>121500</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,86 +6006,89 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10978900</v>
+      </c>
+      <c r="E66" s="3">
         <v>10489900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10407500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9596200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8667100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8018200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7046300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6330800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5641100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6200900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6745800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5721600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4689800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4804700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4875100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4469300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4073700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3679100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3238500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2513600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1987500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1915300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1430600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1189000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>980100</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6256,11 +6424,11 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>1709200</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,86 +6548,89 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6735200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6439300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6094900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-6041900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5951100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-5809200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5684300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5725400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5277700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5133700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5034700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4705500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4199200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-4026900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3570200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3172600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2862000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2486600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2230000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2117800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1891100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1739100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1576100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1552400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1312000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,86 +6952,89 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3976100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4126100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4341800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4212400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4234800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4231400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4284700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4565900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4679500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4864200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5123300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3946200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4505200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5015800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5203700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5449200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5557800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5633100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5807000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6242300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4593400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4859300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4792600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2907100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-1315100</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6867,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-196800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-258700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>54800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-53500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-66700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-91500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-182200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-257700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-176800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-189400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-190000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-532700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-386700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-340200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-332900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-328300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-375500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-236400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-177300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-226700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-169800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-113000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-109600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-298500</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-208600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-151300</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG81" s="3">
-        <v>0</v>
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7246,20 +7445,20 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>138300</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
         <v>63600</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -7274,11 +7473,11 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
         <v>31100</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7288,8 +7487,8 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF83" s="3">
         <v>0</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,8 +8004,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7834,20 +8051,20 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-1160600</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3">
         <v>-317800</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
@@ -7862,11 +8079,11 @@
         <v>0</v>
       </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-68600</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7876,8 +8093,8 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF89" s="3">
         <v>0</v>
@@ -7888,8 +8105,11 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7968,8 +8189,8 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7996,11 +8217,11 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-87000</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8010,8 +8231,8 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8262,20 +8492,20 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>683200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3">
         <v>-249600</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -8290,11 +8520,11 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-897400</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8304,8 +8534,8 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8396,8 +8630,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8788,20 +9034,20 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>846400</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
         <v>239600</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -8816,11 +9062,11 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>2729500</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8830,8 +9076,8 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
@@ -8842,8 +9088,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8886,20 +9135,20 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
         <v>65100</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3">
         <v>4300</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -8914,11 +9163,11 @@
         <v>0</v>
       </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-21400</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
@@ -8928,8 +9177,8 @@
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF101" s="3">
         <v>0</v>
@@ -8940,8 +9189,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8975,8 +9227,8 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
@@ -8985,19 +9237,19 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>434100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3">
         <v>-323500</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
@@ -9012,11 +9264,11 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>1742100</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9026,8 +9278,8 @@
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
+      <c r="AE102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF102" s="3">
         <v>0</v>
@@ -9036,6 +9288,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
